--- a/tame_output/ON/bt/strategyON_20230819.xlsx
+++ b/tame_output/ON/bt/strategyON_20230819.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -911,16 +911,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.8%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>102.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.9%</t>
+          <t>134.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>128.4%</t>
+          <t>128.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1693"/>
+  <dimension ref="A1:G1694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40449,7 +40449,7 @@
         <v>45155</v>
       </c>
       <c r="B1693" t="n">
-        <v>2.783110157528106</v>
+        <v>2.7812949132448</v>
       </c>
       <c r="C1693" t="n">
         <v>2.885591268694849</v>
@@ -40465,6 +40465,29 @@
       </c>
       <c r="G1693" t="n">
         <v>4.192021869799725</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="2" t="n">
+        <v>45156</v>
+      </c>
+      <c r="B1694" t="n">
+        <v>2.764854646391149</v>
+      </c>
+      <c r="C1694" t="n">
+        <v>2.88892904866414</v>
+      </c>
+      <c r="D1694" t="n">
+        <v>1.550942197508523</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>3.508949503353803</v>
+      </c>
+      <c r="F1694" t="n">
+        <v>2.178044708265784</v>
+      </c>
+      <c r="G1694" t="n">
+        <v>4.195755873623613</v>
       </c>
     </row>
   </sheetData>
